--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -14371,7 +14371,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25677,7 +25677,7 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -14371,7 +14371,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25677,7 +25677,7 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -27223,7 +27223,7 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY261"/>
+  <dimension ref="A1:AY262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26753,49 +26753,38 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135357903</v>
+        <v>135519109</v>
       </c>
       <c r="B235" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -26804,13 +26793,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>655565</v>
+        <v>655335</v>
       </c>
       <c r="R235" t="n">
-        <v>7330914</v>
+        <v>7331100</v>
       </c>
       <c r="S235" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26839,7 +26828,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26849,7 +26838,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26864,19 +26853,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135359099</v>
+        <v>135357903</v>
       </c>
       <c r="B236" t="n">
         <v>57162</v>
@@ -26904,20 +26893,36 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>655346</v>
+        <v>655565</v>
       </c>
       <c r="R236" t="n">
-        <v>7331111</v>
+        <v>7330914</v>
       </c>
       <c r="S236" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26946,7 +26951,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26956,12 +26961,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26976,26 +26976,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY236" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135359824</v>
+        <v>135359099</v>
       </c>
       <c r="B237" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27003,21 +26999,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -27027,13 +27023,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>655631</v>
+        <v>655346</v>
       </c>
       <c r="R237" t="n">
-        <v>7330798</v>
+        <v>7331111</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -27062,7 +27058,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27072,7 +27068,12 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27087,12 +27088,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27103,7 +27104,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135363819</v>
+        <v>135359824</v>
       </c>
       <c r="B238" t="n">
         <v>5181</v>
@@ -27132,21 +27133,16 @@
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>655323</v>
+        <v>655631</v>
       </c>
       <c r="R238" t="n">
-        <v>7330913</v>
+        <v>7330798</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -27178,7 +27174,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27188,7 +27184,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27199,31 +27195,16 @@
       </c>
       <c r="AG238" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27234,45 +27215,50 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135359839</v>
+        <v>135363819</v>
       </c>
       <c r="B239" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>655777</v>
+        <v>655323</v>
       </c>
       <c r="R239" t="n">
-        <v>7330820</v>
+        <v>7330913</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -27304,7 +27290,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27314,7 +27300,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27325,16 +27311,31 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -27345,32 +27346,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135356795</v>
+        <v>135359839</v>
       </c>
       <c r="B240" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -27380,10 +27381,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>655319</v>
+        <v>655777</v>
       </c>
       <c r="R240" t="n">
-        <v>7330993</v>
+        <v>7330820</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -27415,7 +27416,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27425,7 +27426,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27440,12 +27441,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -27456,7 +27457,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135363820</v>
+        <v>135356795</v>
       </c>
       <c r="B241" t="n">
         <v>5201</v>
@@ -27485,21 +27486,16 @@
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>655315</v>
+        <v>655319</v>
       </c>
       <c r="R241" t="n">
-        <v>7330919</v>
+        <v>7330993</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -27531,7 +27527,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27541,7 +27537,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27552,31 +27548,16 @@
       </c>
       <c r="AG241" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -27587,27 +27568,27 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135359792</v>
+        <v>135363820</v>
       </c>
       <c r="B242" t="n">
-        <v>56706</v>
+        <v>5201</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>206046</v>
+        <v>105930</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -27616,16 +27597,21 @@
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>655330</v>
+        <v>655315</v>
       </c>
       <c r="R242" t="n">
-        <v>7330904</v>
+        <v>7330919</v>
       </c>
       <c r="S242" t="n">
         <v>5</v>
@@ -27657,7 +27643,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27667,7 +27653,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27678,16 +27664,31 @@
       </c>
       <c r="AG242" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27698,32 +27699,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135363827</v>
+        <v>135359792</v>
       </c>
       <c r="B243" t="n">
-        <v>99197</v>
+        <v>56706</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>219811</v>
+        <v>206046</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27733,10 +27734,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>655525</v>
+        <v>655330</v>
       </c>
       <c r="R243" t="n">
-        <v>7330820</v>
+        <v>7330904</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -27768,7 +27769,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27778,7 +27779,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27793,12 +27794,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -27809,10 +27810,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135357398</v>
+        <v>135363827</v>
       </c>
       <c r="B244" t="n">
-        <v>99099</v>
+        <v>99197</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27820,21 +27821,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27844,10 +27845,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>655579</v>
+        <v>655525</v>
       </c>
       <c r="R244" t="n">
-        <v>7330863</v>
+        <v>7330820</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -27879,7 +27880,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27889,7 +27890,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27904,12 +27905,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27920,7 +27921,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135357400</v>
+        <v>135357398</v>
       </c>
       <c r="B245" t="n">
         <v>99099</v>
@@ -27955,13 +27956,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R245" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27990,7 +27991,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -28000,7 +28001,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28031,7 +28032,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135359822</v>
+        <v>135357400</v>
       </c>
       <c r="B246" t="n">
         <v>99099</v>
@@ -28066,13 +28067,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>655610</v>
+        <v>655621</v>
       </c>
       <c r="R246" t="n">
-        <v>7330795</v>
+        <v>7330834</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28101,7 +28102,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28111,7 +28112,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28126,12 +28127,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -28142,10 +28143,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135357395</v>
+        <v>135359822</v>
       </c>
       <c r="B247" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28153,21 +28154,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28177,13 +28178,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>655546</v>
+        <v>655610</v>
       </c>
       <c r="R247" t="n">
-        <v>7330858</v>
+        <v>7330795</v>
       </c>
       <c r="S247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28212,7 +28213,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28222,7 +28223,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28237,12 +28238,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -28253,7 +28254,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135357397</v>
+        <v>135357395</v>
       </c>
       <c r="B248" t="n">
         <v>99217</v>
@@ -28288,13 +28289,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>655579</v>
+        <v>655546</v>
       </c>
       <c r="R248" t="n">
-        <v>7330863</v>
+        <v>7330858</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28323,7 +28324,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28333,7 +28334,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28364,7 +28365,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135357399</v>
+        <v>135357397</v>
       </c>
       <c r="B249" t="n">
         <v>99217</v>
@@ -28399,13 +28400,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R249" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S249" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28434,7 +28435,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28444,7 +28445,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28475,7 +28476,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135357401</v>
+        <v>135357399</v>
       </c>
       <c r="B250" t="n">
         <v>99217</v>
@@ -28510,13 +28511,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>655806</v>
+        <v>655621</v>
       </c>
       <c r="R250" t="n">
-        <v>7330742</v>
+        <v>7330834</v>
       </c>
       <c r="S250" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28545,7 +28546,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28555,7 +28556,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28586,7 +28587,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135357402</v>
+        <v>135357401</v>
       </c>
       <c r="B251" t="n">
         <v>99217</v>
@@ -28621,10 +28622,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>655842</v>
+        <v>655806</v>
       </c>
       <c r="R251" t="n">
-        <v>7330740</v>
+        <v>7330742</v>
       </c>
       <c r="S251" t="n">
         <v>5</v>
@@ -28656,7 +28657,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28666,7 +28667,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28697,7 +28698,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135357403</v>
+        <v>135357402</v>
       </c>
       <c r="B252" t="n">
         <v>99217</v>
@@ -28732,10 +28733,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>655735</v>
+        <v>655842</v>
       </c>
       <c r="R252" t="n">
-        <v>7330853</v>
+        <v>7330740</v>
       </c>
       <c r="S252" t="n">
         <v>5</v>
@@ -28767,7 +28768,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28777,7 +28778,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28808,7 +28809,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135357405</v>
+        <v>135357403</v>
       </c>
       <c r="B253" t="n">
         <v>99217</v>
@@ -28843,13 +28844,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>655649</v>
+        <v>655735</v>
       </c>
       <c r="R253" t="n">
-        <v>7330872</v>
+        <v>7330853</v>
       </c>
       <c r="S253" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28878,7 +28879,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28888,7 +28889,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28919,7 +28920,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135357406</v>
+        <v>135357405</v>
       </c>
       <c r="B254" t="n">
         <v>99217</v>
@@ -28954,13 +28955,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>655448</v>
+        <v>655649</v>
       </c>
       <c r="R254" t="n">
-        <v>7330951</v>
+        <v>7330872</v>
       </c>
       <c r="S254" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28989,7 +28990,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28999,7 +29000,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29030,7 +29031,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135359811</v>
+        <v>135357406</v>
       </c>
       <c r="B255" t="n">
         <v>99217</v>
@@ -29065,13 +29066,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>655554</v>
+        <v>655448</v>
       </c>
       <c r="R255" t="n">
-        <v>7330834</v>
+        <v>7330951</v>
       </c>
       <c r="S255" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -29100,7 +29101,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29110,12 +29111,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29130,12 +29126,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -29146,7 +29142,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135359812</v>
+        <v>135359811</v>
       </c>
       <c r="B256" t="n">
         <v>99217</v>
@@ -29181,13 +29177,13 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>655568</v>
+        <v>655554</v>
       </c>
       <c r="R256" t="n">
-        <v>7330829</v>
+        <v>7330834</v>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29216,7 +29212,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -29226,12 +29222,12 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>4 exemplar</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29262,7 +29258,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135359813</v>
+        <v>135359812</v>
       </c>
       <c r="B257" t="n">
         <v>99217</v>
@@ -29297,13 +29293,13 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>655571</v>
+        <v>655568</v>
       </c>
       <c r="R257" t="n">
-        <v>7330837</v>
+        <v>7330829</v>
       </c>
       <c r="S257" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29332,7 +29328,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -29342,12 +29338,12 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>4 exemplar</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29378,7 +29374,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135359821</v>
+        <v>135359813</v>
       </c>
       <c r="B258" t="n">
         <v>99217</v>
@@ -29413,13 +29409,13 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>655613</v>
+        <v>655571</v>
       </c>
       <c r="R258" t="n">
-        <v>7330794</v>
+        <v>7330837</v>
       </c>
       <c r="S258" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29448,7 +29444,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -29458,7 +29454,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
@@ -29494,7 +29490,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135359838</v>
+        <v>135359821</v>
       </c>
       <c r="B259" t="n">
         <v>99217</v>
@@ -29529,10 +29525,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>655778</v>
+        <v>655613</v>
       </c>
       <c r="R259" t="n">
-        <v>7330823</v>
+        <v>7330794</v>
       </c>
       <c r="S259" t="n">
         <v>5</v>
@@ -29564,7 +29560,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -29574,7 +29570,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
@@ -29610,7 +29606,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135359851</v>
+        <v>135359838</v>
       </c>
       <c r="B260" t="n">
         <v>99217</v>
@@ -29645,13 +29641,13 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>655429</v>
+        <v>655778</v>
       </c>
       <c r="R260" t="n">
-        <v>7330949</v>
+        <v>7330823</v>
       </c>
       <c r="S260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29680,7 +29676,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29690,7 +29686,12 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29721,7 +29722,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>135363823</v>
+        <v>135359851</v>
       </c>
       <c r="B261" t="n">
         <v>99217</v>
@@ -29756,13 +29757,13 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>655537</v>
+        <v>655429</v>
       </c>
       <c r="R261" t="n">
-        <v>7330838</v>
+        <v>7330949</v>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29791,7 +29792,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -29801,7 +29802,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29816,15 +29817,126 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>135363823</v>
+      </c>
+      <c r="B262" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>655537</v>
+      </c>
+      <c r="R262" t="n">
+        <v>7330838</v>
+      </c>
+      <c r="S262" t="n">
+        <v>5</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX261" t="inlineStr">
+      <c r="AX262" t="inlineStr">
         <is>
           <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
-      <c r="AY261" t="inlineStr">
+      <c r="AY262" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -26782,11 +26782,14 @@
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
@@ -26861,7 +26864,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY235" t="inlineStr"/>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY262"/>
+  <dimension ref="A1:AZ262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357743</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357390</t>
         </is>
       </c>
     </row>
@@ -1014,6 +1029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359820</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357874</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356794</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357582</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357587</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357591</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2358,6 +2433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2474,6 +2554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357608</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2590,6 +2675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357630</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2697,6 +2787,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357852</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2798,6 +2893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358259</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358264</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3015,6 +3120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359833</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3126,6 +3236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362040</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3237,6 +3352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362050</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3349,6 +3469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362051</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3460,6 +3585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362060</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3571,6 +3701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362061</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3678,6 +3813,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357881</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3802,6 +3942,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363826</t>
         </is>
       </c>
     </row>
@@ -3919,6 +4064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357752</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4026,6 +4176,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357856</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4133,6 +4288,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357859</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4240,6 +4400,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357873</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4347,6 +4512,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357875</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4454,6 +4624,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357882</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4561,6 +4736,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357898</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4670,6 +4850,11 @@
       <c r="AY37" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359825</t>
         </is>
       </c>
     </row>
@@ -4792,6 +4977,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357751</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4903,6 +5093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359815</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5014,6 +5209,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357389</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5125,6 +5325,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359785</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5236,6 +5441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359788</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5347,6 +5557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359798</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5458,6 +5673,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359817</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5569,6 +5789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359819</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5680,6 +5905,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359834</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5791,6 +6021,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359835</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5902,6 +6137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359848</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6013,6 +6253,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359852</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6125,6 +6370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357396</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6234,6 +6484,11 @@
       <c r="AY51" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359850</t>
         </is>
       </c>
     </row>
@@ -6351,6 +6606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388328</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6448,6 +6708,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313467</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6559,6 +6824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356789</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6670,6 +6940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356791</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6781,6 +7056,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356793</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6892,6 +7172,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356798</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7003,6 +7288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356801</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7114,6 +7404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356804</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7225,6 +7520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356805</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7336,6 +7636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356806</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7447,6 +7752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356807</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7558,6 +7868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356808</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7669,6 +7984,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357388</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7780,6 +8100,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357392</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7891,6 +8216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357394</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8002,6 +8332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357404</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8118,6 +8453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357576</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8229,6 +8569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357577</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8340,6 +8685,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357580</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8451,6 +8801,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357581</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8562,6 +8917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357583</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8673,6 +9033,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357584</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8784,6 +9149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357586</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8895,6 +9265,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357589</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9006,6 +9381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357590</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9117,6 +9497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357592</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9228,6 +9613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357594</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9339,6 +9729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357595</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9450,6 +9845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357596</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9561,6 +9961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357598</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9672,6 +10077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357601</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9783,6 +10193,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357604</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9894,6 +10309,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357605</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10010,6 +10430,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357607</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10121,6 +10546,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357609</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10232,6 +10662,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357610</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10343,6 +10778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357612</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10454,6 +10894,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357613</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10565,6 +11010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357614</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10676,6 +11126,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357615</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10787,6 +11242,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357616</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10898,6 +11358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357617</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11009,6 +11474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357618</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11120,6 +11590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357620</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11231,6 +11706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357621</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11342,6 +11822,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357622</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11453,6 +11938,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357623</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11564,6 +12054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357624</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11675,6 +12170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357625</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11786,6 +12286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357627</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11897,6 +12402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357628</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12008,6 +12518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357631</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12119,6 +12634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357736</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12230,6 +12750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357737</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12341,6 +12866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357740</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12452,6 +12982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357750</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12559,6 +13094,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357853</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12666,6 +13206,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357854</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12773,6 +13318,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357858</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12885,6 +13435,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357866</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12997,6 +13552,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357867</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13104,6 +13664,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357872</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13211,6 +13776,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357878</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13318,6 +13888,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357883</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13425,6 +14000,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357889</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13532,6 +14112,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357896</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13639,6 +14224,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357897</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13746,6 +14336,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357899</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13853,6 +14448,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357900</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13960,6 +14560,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357901</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14061,6 +14666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358261</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14162,6 +14772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358262</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14263,6 +14878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358263</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14379,6 +14999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359086</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14495,6 +15120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359087</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14611,6 +15241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359088</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14727,6 +15362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359089</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14843,6 +15483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359090</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14959,6 +15604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359091</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15075,6 +15725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359092</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15191,6 +15846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359093</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15307,6 +15967,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359095</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15421,6 +16086,11 @@
       <c r="AY134" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359097</t>
         </is>
       </c>
     </row>
@@ -15538,6 +16208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359781</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15649,6 +16324,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359787</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15760,6 +16440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359789</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15872,6 +16557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359793</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15983,6 +16673,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359795</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16094,6 +16789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359796</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16205,6 +16905,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359797</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16316,6 +17021,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359799</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16427,6 +17137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359801</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16538,6 +17253,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359804</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16649,6 +17369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359805</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16760,6 +17485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359809</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16871,6 +17601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359810</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16982,6 +17717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359816</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17093,6 +17833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359818</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17204,6 +17949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359823</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17315,6 +18065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359829</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17426,6 +18181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359832</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17537,6 +18297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359837</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17648,6 +18413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359849</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17759,6 +18529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362032</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17870,6 +18645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362033</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17981,6 +18761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362036</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18092,6 +18877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362038</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18203,6 +18993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362039</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18314,6 +19109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362044</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18425,6 +19225,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362047</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18536,6 +19341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362048</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18647,6 +19457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362055</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18758,6 +19573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362056</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18869,6 +19689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362058</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18980,6 +19805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362062</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19091,6 +19921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362063</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19202,6 +20037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362066</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19313,6 +20153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363825</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19424,6 +20269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357733</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19535,6 +20385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357735</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19646,6 +20501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359836</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19757,6 +20617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356790</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19868,6 +20733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356797</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19977,6 +20847,11 @@
       <c r="AY175" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356800</t>
         </is>
       </c>
     </row>
@@ -20094,6 +20969,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357739</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20210,6 +21090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359085</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20321,6 +21206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359830</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20432,6 +21322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359831</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20548,6 +21443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359098</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20659,6 +21559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362041</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20770,6 +21675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357746</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20881,6 +21791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357748</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20992,6 +21907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359827</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21103,6 +22023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359842</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21214,6 +22139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359846</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21325,6 +22255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357747</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21436,6 +22371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359841</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21547,6 +22487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359845</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21658,6 +22603,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359826</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21769,6 +22719,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359843</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21880,6 +22835,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359847</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21989,6 +22949,11 @@
       <c r="AY193" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362052</t>
         </is>
       </c>
     </row>
@@ -22106,6 +23071,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362054</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22222,6 +23192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359096</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22338,6 +23313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359853</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22457,6 +23437,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362037</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22576,6 +23561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362049</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22678,6 +23668,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313304</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22780,6 +23775,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313442</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22896,6 +23896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357407</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23012,6 +24017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357579</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23128,6 +24138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357588</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23244,6 +24259,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357626</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23360,6 +24380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357734</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23476,6 +24501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357742</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23592,6 +24622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357749</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23709,6 +24744,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357857</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23826,6 +24866,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357861</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23943,6 +24988,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357863</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24060,6 +25110,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357864</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24177,6 +25232,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357865</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24294,6 +25354,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357869</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24411,6 +25476,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357879</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24528,6 +25598,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357885</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24645,6 +25720,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357888</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24762,6 +25842,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357890</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24879,6 +25964,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357891</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24996,6 +26086,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357892</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25113,6 +26208,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357894</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25230,6 +26330,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357902</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25347,6 +26452,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357906</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25453,6 +26563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358260</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25569,6 +26684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359094</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25685,6 +26805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359100</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25801,6 +26926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359784</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25917,6 +27047,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359803</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26036,6 +27171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362035</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26155,6 +27295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362042</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26274,6 +27419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362043</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26393,6 +27543,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362057</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26512,6 +27667,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362059</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26631,6 +27791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362064</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26750,6 +27915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362065</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26869,6 +28039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135519109</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26992,6 +28167,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357903</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27108,6 +28288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359099</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27219,6 +28404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359824</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27350,6 +28540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363819</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27461,6 +28656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359839</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27572,6 +28772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356795</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27703,6 +28908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363820</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27814,6 +29024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359792</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27925,6 +29140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363827</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28036,6 +29256,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357398</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28147,6 +29372,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357400</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28258,6 +29488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359822</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28369,6 +29604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357395</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28480,6 +29720,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357397</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28591,6 +29836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357399</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28702,6 +29952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357401</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28813,6 +30068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357402</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28924,6 +30184,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357403</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29035,6 +30300,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357405</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29146,6 +30416,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357406</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29262,6 +30537,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359811</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29378,6 +30658,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359812</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29494,6 +30779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359813</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29610,6 +30900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359821</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29726,6 +31021,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359838</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29837,6 +31137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359851</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29948,8 +31253,276 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363823</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357743</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135357390</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135357753</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135359820</v>
       </c>
       <c r="B5" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135356799</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135357874</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135357745</v>
       </c>
       <c r="B8" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135313461</v>
       </c>
       <c r="B9" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135356794</v>
       </c>
       <c r="B10" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135356802</v>
       </c>
       <c r="B11" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>135356803</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135357582</v>
       </c>
       <c r="B13" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>135357587</v>
       </c>
       <c r="B14" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>135357591</v>
       </c>
       <c r="B15" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135357600</v>
       </c>
       <c r="B16" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135357608</v>
       </c>
       <c r="B17" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135357630</v>
       </c>
       <c r="B18" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135357852</v>
       </c>
       <c r="B19" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135358259</v>
       </c>
       <c r="B20" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>135358264</v>
       </c>
       <c r="B21" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>135359833</v>
       </c>
       <c r="B22" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>135362040</v>
       </c>
       <c r="B23" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135362050</v>
       </c>
       <c r="B24" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>135362051</v>
       </c>
       <c r="B25" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135362060</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135362061</v>
       </c>
       <c r="B27" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135357881</v>
       </c>
       <c r="B28" t="n">
-        <v>92689</v>
+        <v>92731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135363826</v>
       </c>
       <c r="B29" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>135357752</v>
       </c>
       <c r="B30" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135357856</v>
       </c>
       <c r="B31" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>135357859</v>
       </c>
       <c r="B32" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135357873</v>
       </c>
       <c r="B33" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>135357875</v>
       </c>
       <c r="B34" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>135357882</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>135357898</v>
       </c>
       <c r="B36" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>135359825</v>
       </c>
       <c r="B37" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>135357751</v>
       </c>
       <c r="B38" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135359815</v>
       </c>
       <c r="B39" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>135357389</v>
       </c>
       <c r="B40" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135359785</v>
       </c>
       <c r="B41" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135359788</v>
       </c>
       <c r="B42" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>135359798</v>
       </c>
       <c r="B43" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>135359817</v>
       </c>
       <c r="B44" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>135359819</v>
       </c>
       <c r="B45" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>135359834</v>
       </c>
       <c r="B46" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>135359835</v>
       </c>
       <c r="B47" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>135359848</v>
       </c>
       <c r="B48" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135359852</v>
       </c>
       <c r="B49" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>135357396</v>
       </c>
       <c r="B50" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>135359850</v>
       </c>
       <c r="B51" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135388328</v>
       </c>
       <c r="B52" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135313467</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>135356789</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>135356791</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>135356793</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>135356798</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135356801</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>135356804</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>135356805</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135356806</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>135356807</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>135356808</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>135357388</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>135357392</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>135357394</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>135357404</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>135357576</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>135357577</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>135357580</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>135357581</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>135357583</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>135357584</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>135357586</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>135357589</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>135357590</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>135357592</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>135357594</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>135357595</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>135357596</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135357598</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>135357601</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135357604</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>135357605</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>135357607</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>135357609</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>135357610</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>135357612</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>135357613</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>135357614</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135357615</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>135357616</v>
       </c>
       <c r="B92" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>135357617</v>
       </c>
       <c r="B93" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>135357618</v>
       </c>
       <c r="B94" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>135357620</v>
       </c>
       <c r="B95" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>135357621</v>
       </c>
       <c r="B96" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>135357622</v>
       </c>
       <c r="B97" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>135357623</v>
       </c>
       <c r="B98" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135357624</v>
       </c>
       <c r="B99" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>135357625</v>
       </c>
       <c r="B100" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>135357627</v>
       </c>
       <c r="B101" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>135357628</v>
       </c>
       <c r="B102" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>135357631</v>
       </c>
       <c r="B103" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>135357736</v>
       </c>
       <c r="B104" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>135357737</v>
       </c>
       <c r="B105" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>135357740</v>
       </c>
       <c r="B106" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>135357750</v>
       </c>
       <c r="B107" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135357853</v>
       </c>
       <c r="B108" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>135357854</v>
       </c>
       <c r="B109" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>135357858</v>
       </c>
       <c r="B110" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>135357866</v>
       </c>
       <c r="B111" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>135357867</v>
       </c>
       <c r="B112" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>135357872</v>
       </c>
       <c r="B113" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135357878</v>
       </c>
       <c r="B114" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>135357883</v>
       </c>
       <c r="B115" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>135357889</v>
       </c>
       <c r="B116" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>135357896</v>
       </c>
       <c r="B117" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>135357897</v>
       </c>
       <c r="B118" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>135357899</v>
       </c>
       <c r="B119" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>135357900</v>
       </c>
       <c r="B120" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>135357901</v>
       </c>
       <c r="B121" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>135358261</v>
       </c>
       <c r="B122" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>135358262</v>
       </c>
       <c r="B123" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>135358263</v>
       </c>
       <c r="B124" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>135359086</v>
       </c>
       <c r="B125" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>135359087</v>
       </c>
       <c r="B126" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>135359088</v>
       </c>
       <c r="B127" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>135359089</v>
       </c>
       <c r="B128" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>135359090</v>
       </c>
       <c r="B129" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>135359091</v>
       </c>
       <c r="B130" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>135359092</v>
       </c>
       <c r="B131" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>135359093</v>
       </c>
       <c r="B132" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>135359095</v>
       </c>
       <c r="B133" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>135359097</v>
       </c>
       <c r="B134" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>135359781</v>
       </c>
       <c r="B135" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>135359787</v>
       </c>
       <c r="B136" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>135359789</v>
       </c>
       <c r="B137" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>135359793</v>
       </c>
       <c r="B138" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>135359795</v>
       </c>
       <c r="B139" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>135359796</v>
       </c>
       <c r="B140" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>135359797</v>
       </c>
       <c r="B141" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>135359799</v>
       </c>
       <c r="B142" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>135359801</v>
       </c>
       <c r="B143" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>135359804</v>
       </c>
       <c r="B144" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>135359805</v>
       </c>
       <c r="B145" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>135359809</v>
       </c>
       <c r="B146" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>135359810</v>
       </c>
       <c r="B147" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>135359816</v>
       </c>
       <c r="B148" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135359818</v>
       </c>
       <c r="B149" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>135359823</v>
       </c>
       <c r="B150" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>135359829</v>
       </c>
       <c r="B151" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>135359832</v>
       </c>
       <c r="B152" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>135359837</v>
       </c>
       <c r="B153" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>135359849</v>
       </c>
       <c r="B154" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>135362032</v>
       </c>
       <c r="B155" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>135362033</v>
       </c>
       <c r="B156" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>135362036</v>
       </c>
       <c r="B157" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135362038</v>
       </c>
       <c r="B158" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>135362039</v>
       </c>
       <c r="B159" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>135362044</v>
       </c>
       <c r="B160" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135362047</v>
       </c>
       <c r="B161" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>135362048</v>
       </c>
       <c r="B162" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>135362055</v>
       </c>
       <c r="B163" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>135362056</v>
       </c>
       <c r="B164" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>135362058</v>
       </c>
       <c r="B165" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135362062</v>
       </c>
       <c r="B166" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>135362063</v>
       </c>
       <c r="B167" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>135362066</v>
       </c>
       <c r="B168" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>135363825</v>
       </c>
       <c r="B169" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>135357733</v>
       </c>
       <c r="B170" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>135357735</v>
       </c>
       <c r="B171" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>135359836</v>
       </c>
       <c r="B172" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>135356790</v>
       </c>
       <c r="B173" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>135356797</v>
       </c>
       <c r="B174" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>135356800</v>
       </c>
       <c r="B175" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>135357739</v>
       </c>
       <c r="B176" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>135359085</v>
       </c>
       <c r="B177" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>135359830</v>
       </c>
       <c r="B178" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>135359831</v>
       </c>
       <c r="B179" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>135359098</v>
       </c>
       <c r="B180" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>135362041</v>
       </c>
       <c r="B181" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>135357746</v>
       </c>
       <c r="B182" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>135357748</v>
       </c>
       <c r="B183" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>135359827</v>
       </c>
       <c r="B184" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>135359842</v>
       </c>
       <c r="B185" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>135359846</v>
       </c>
       <c r="B186" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>135357747</v>
       </c>
       <c r="B187" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>135359841</v>
       </c>
       <c r="B188" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135359845</v>
       </c>
       <c r="B189" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>135359826</v>
       </c>
       <c r="B190" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>135359843</v>
       </c>
       <c r="B191" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>135359847</v>
       </c>
       <c r="B192" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>135362052</v>
       </c>
       <c r="B193" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>135362054</v>
       </c>
       <c r="B194" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>135359096</v>
       </c>
       <c r="B195" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>135359853</v>
       </c>
       <c r="B196" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>135362037</v>
       </c>
       <c r="B197" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>135362049</v>
       </c>
       <c r="B198" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>135313304</v>
       </c>
       <c r="B199" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>135313442</v>
       </c>
       <c r="B200" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>135357407</v>
       </c>
       <c r="B201" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>135357579</v>
       </c>
       <c r="B202" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>135357588</v>
       </c>
       <c r="B203" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>135357626</v>
       </c>
       <c r="B204" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>135357734</v>
       </c>
       <c r="B205" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>135357742</v>
       </c>
       <c r="B206" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>135357749</v>
       </c>
       <c r="B207" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>135357857</v>
       </c>
       <c r="B208" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>135357861</v>
       </c>
       <c r="B209" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>135357863</v>
       </c>
       <c r="B210" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>135357864</v>
       </c>
       <c r="B211" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>135357865</v>
       </c>
       <c r="B212" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>135357869</v>
       </c>
       <c r="B213" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>135357879</v>
       </c>
       <c r="B214" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>135357885</v>
       </c>
       <c r="B215" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>135357888</v>
       </c>
       <c r="B216" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>135357890</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>135357891</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>135357892</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>135357894</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>135357902</v>
       </c>
       <c r="B221" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>135357906</v>
       </c>
       <c r="B222" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>135358260</v>
       </c>
       <c r="B223" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>135359094</v>
       </c>
       <c r="B224" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>135359100</v>
       </c>
       <c r="B225" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>135359784</v>
       </c>
       <c r="B226" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>135359803</v>
       </c>
       <c r="B227" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>135362035</v>
       </c>
       <c r="B228" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>135362042</v>
       </c>
       <c r="B229" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>135362043</v>
       </c>
       <c r="B230" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>135362057</v>
       </c>
       <c r="B231" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>135362059</v>
       </c>
       <c r="B232" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>135362064</v>
       </c>
       <c r="B233" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>135362065</v>
       </c>
       <c r="B234" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>135519109</v>
       </c>
       <c r="B235" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>135357903</v>
       </c>
       <c r="B236" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>135359099</v>
       </c>
       <c r="B237" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>135359839</v>
       </c>
       <c r="B240" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>135359792</v>
       </c>
       <c r="B243" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>135363827</v>
       </c>
       <c r="B244" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>135357398</v>
       </c>
       <c r="B245" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>135357400</v>
       </c>
       <c r="B246" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>135359822</v>
       </c>
       <c r="B247" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>135357395</v>
       </c>
       <c r="B248" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>135357397</v>
       </c>
       <c r="B249" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>135357399</v>
       </c>
       <c r="B250" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>135357401</v>
       </c>
       <c r="B251" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>135357402</v>
       </c>
       <c r="B252" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>135357403</v>
       </c>
       <c r="B253" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>135357405</v>
       </c>
       <c r="B254" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>135357406</v>
       </c>
       <c r="B255" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>135359811</v>
       </c>
       <c r="B256" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>135359812</v>
       </c>
       <c r="B257" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>135359813</v>
       </c>
       <c r="B258" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135359821</v>
       </c>
       <c r="B259" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>135359838</v>
       </c>
       <c r="B260" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>135359851</v>
       </c>
       <c r="B261" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>135363823</v>
       </c>
       <c r="B262" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357743</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135357390</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135357753</v>
       </c>
       <c r="B4" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135359820</v>
       </c>
       <c r="B5" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135356799</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135357874</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135357745</v>
       </c>
       <c r="B8" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135313461</v>
       </c>
       <c r="B9" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135356794</v>
       </c>
       <c r="B10" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135356802</v>
       </c>
       <c r="B11" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>135356803</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135357582</v>
       </c>
       <c r="B13" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>135357587</v>
       </c>
       <c r="B14" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>135357591</v>
       </c>
       <c r="B15" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>135357600</v>
       </c>
       <c r="B16" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135357608</v>
       </c>
       <c r="B17" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135357630</v>
       </c>
       <c r="B18" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135357852</v>
       </c>
       <c r="B19" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135358259</v>
       </c>
       <c r="B20" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>135358264</v>
       </c>
       <c r="B21" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>135359833</v>
       </c>
       <c r="B22" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>135362040</v>
       </c>
       <c r="B23" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135362050</v>
       </c>
       <c r="B24" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>135362051</v>
       </c>
       <c r="B25" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135362060</v>
       </c>
       <c r="B26" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135362061</v>
       </c>
       <c r="B27" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135357881</v>
       </c>
       <c r="B28" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135363826</v>
       </c>
       <c r="B29" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>135357752</v>
       </c>
       <c r="B30" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135357856</v>
       </c>
       <c r="B31" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>135357859</v>
       </c>
       <c r="B32" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135357873</v>
       </c>
       <c r="B33" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>135357875</v>
       </c>
       <c r="B34" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>135357882</v>
       </c>
       <c r="B35" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>135357898</v>
       </c>
       <c r="B36" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>135359825</v>
       </c>
       <c r="B37" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>135357751</v>
       </c>
       <c r="B38" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135359815</v>
       </c>
       <c r="B39" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>135357389</v>
       </c>
       <c r="B40" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135359785</v>
       </c>
       <c r="B41" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135359788</v>
       </c>
       <c r="B42" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>135359798</v>
       </c>
       <c r="B43" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>135359817</v>
       </c>
       <c r="B44" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>135359819</v>
       </c>
       <c r="B45" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>135359834</v>
       </c>
       <c r="B46" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>135359835</v>
       </c>
       <c r="B47" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>135359848</v>
       </c>
       <c r="B48" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135359852</v>
       </c>
       <c r="B49" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>135357396</v>
       </c>
       <c r="B50" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>135359850</v>
       </c>
       <c r="B51" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135388328</v>
       </c>
       <c r="B52" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135313467</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>135356789</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>135356791</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>135356793</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>135356798</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135356801</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>135356804</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>135356805</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135356806</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>135356807</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>135356808</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>135357388</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>135357392</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>135357394</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>135357404</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>135357576</v>
       </c>
       <c r="B68" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>135357577</v>
       </c>
       <c r="B69" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>135357580</v>
       </c>
       <c r="B70" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>135357581</v>
       </c>
       <c r="B71" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>135357583</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>135357584</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>135357586</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>135357589</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>135357590</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>135357592</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>135357594</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>135357595</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>135357596</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135357598</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>135357601</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135357604</v>
       </c>
       <c r="B83" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>135357605</v>
       </c>
       <c r="B84" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>135357607</v>
       </c>
       <c r="B85" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>135357609</v>
       </c>
       <c r="B86" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>135357610</v>
       </c>
       <c r="B87" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>135357612</v>
       </c>
       <c r="B88" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>135357613</v>
       </c>
       <c r="B89" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>135357614</v>
       </c>
       <c r="B90" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135357615</v>
       </c>
       <c r="B91" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>135357616</v>
       </c>
       <c r="B92" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>135357617</v>
       </c>
       <c r="B93" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>135357618</v>
       </c>
       <c r="B94" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>135357620</v>
       </c>
       <c r="B95" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>135357621</v>
       </c>
       <c r="B96" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>135357622</v>
       </c>
       <c r="B97" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>135357623</v>
       </c>
       <c r="B98" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135357624</v>
       </c>
       <c r="B99" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>135357625</v>
       </c>
       <c r="B100" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>135357627</v>
       </c>
       <c r="B101" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>135357628</v>
       </c>
       <c r="B102" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>135357631</v>
       </c>
       <c r="B103" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>135357736</v>
       </c>
       <c r="B104" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>135357737</v>
       </c>
       <c r="B105" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>135357740</v>
       </c>
       <c r="B106" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>135357750</v>
       </c>
       <c r="B107" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135357853</v>
       </c>
       <c r="B108" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>135357854</v>
       </c>
       <c r="B109" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>135357858</v>
       </c>
       <c r="B110" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>135357866</v>
       </c>
       <c r="B111" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>135357867</v>
       </c>
       <c r="B112" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>135357872</v>
       </c>
       <c r="B113" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135357878</v>
       </c>
       <c r="B114" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>135357883</v>
       </c>
       <c r="B115" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>135357889</v>
       </c>
       <c r="B116" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>135357896</v>
       </c>
       <c r="B117" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>135357897</v>
       </c>
       <c r="B118" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>135357899</v>
       </c>
       <c r="B119" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>135357900</v>
       </c>
       <c r="B120" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>135357901</v>
       </c>
       <c r="B121" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>135358261</v>
       </c>
       <c r="B122" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>135358262</v>
       </c>
       <c r="B123" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>135358263</v>
       </c>
       <c r="B124" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>135359086</v>
       </c>
       <c r="B125" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>135359087</v>
       </c>
       <c r="B126" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>135359088</v>
       </c>
       <c r="B127" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>135359089</v>
       </c>
       <c r="B128" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>135359090</v>
       </c>
       <c r="B129" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>135359091</v>
       </c>
       <c r="B130" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>135359092</v>
       </c>
       <c r="B131" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>135359093</v>
       </c>
       <c r="B132" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>135359095</v>
       </c>
       <c r="B133" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>135359097</v>
       </c>
       <c r="B134" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>135359781</v>
       </c>
       <c r="B135" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>135359787</v>
       </c>
       <c r="B136" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>135359789</v>
       </c>
       <c r="B137" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>135359793</v>
       </c>
       <c r="B138" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>135359795</v>
       </c>
       <c r="B139" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>135359796</v>
       </c>
       <c r="B140" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>135359797</v>
       </c>
       <c r="B141" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>135359799</v>
       </c>
       <c r="B142" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>135359801</v>
       </c>
       <c r="B143" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>135359804</v>
       </c>
       <c r="B144" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>135359805</v>
       </c>
       <c r="B145" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>135359809</v>
       </c>
       <c r="B146" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>135359810</v>
       </c>
       <c r="B147" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>135359816</v>
       </c>
       <c r="B148" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135359818</v>
       </c>
       <c r="B149" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>135359823</v>
       </c>
       <c r="B150" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>135359829</v>
       </c>
       <c r="B151" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>135359832</v>
       </c>
       <c r="B152" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>135359837</v>
       </c>
       <c r="B153" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>135359849</v>
       </c>
       <c r="B154" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>135362032</v>
       </c>
       <c r="B155" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>135362033</v>
       </c>
       <c r="B156" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>135362036</v>
       </c>
       <c r="B157" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135362038</v>
       </c>
       <c r="B158" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>135362039</v>
       </c>
       <c r="B159" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>135362044</v>
       </c>
       <c r="B160" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135362047</v>
       </c>
       <c r="B161" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>135362048</v>
       </c>
       <c r="B162" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>135362055</v>
       </c>
       <c r="B163" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>135362056</v>
       </c>
       <c r="B164" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>135362058</v>
       </c>
       <c r="B165" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135362062</v>
       </c>
       <c r="B166" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>135362063</v>
       </c>
       <c r="B167" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>135362066</v>
       </c>
       <c r="B168" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>135363825</v>
       </c>
       <c r="B169" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>135357733</v>
       </c>
       <c r="B170" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>135357735</v>
       </c>
       <c r="B171" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>135359836</v>
       </c>
       <c r="B172" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>135356790</v>
       </c>
       <c r="B173" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>135356797</v>
       </c>
       <c r="B174" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>135356800</v>
       </c>
       <c r="B175" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>135357739</v>
       </c>
       <c r="B176" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>135359085</v>
       </c>
       <c r="B177" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>135359830</v>
       </c>
       <c r="B178" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>135359831</v>
       </c>
       <c r="B179" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>135359098</v>
       </c>
       <c r="B180" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>135362041</v>
       </c>
       <c r="B181" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>135357746</v>
       </c>
       <c r="B182" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>135357748</v>
       </c>
       <c r="B183" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>135359827</v>
       </c>
       <c r="B184" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>135359842</v>
       </c>
       <c r="B185" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>135359846</v>
       </c>
       <c r="B186" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>135357747</v>
       </c>
       <c r="B187" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>135359841</v>
       </c>
       <c r="B188" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135359845</v>
       </c>
       <c r="B189" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>135359826</v>
       </c>
       <c r="B190" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>135359843</v>
       </c>
       <c r="B191" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>135359847</v>
       </c>
       <c r="B192" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>135362052</v>
       </c>
       <c r="B193" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>135363827</v>
       </c>
       <c r="B244" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>135357398</v>
       </c>
       <c r="B245" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>135357400</v>
       </c>
       <c r="B246" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>135359822</v>
       </c>
       <c r="B247" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>135357395</v>
       </c>
       <c r="B248" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>135357397</v>
       </c>
       <c r="B249" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>135357399</v>
       </c>
       <c r="B250" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>135357401</v>
       </c>
       <c r="B251" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>135357402</v>
       </c>
       <c r="B252" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>135357403</v>
       </c>
       <c r="B253" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>135357405</v>
       </c>
       <c r="B254" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>135357406</v>
       </c>
       <c r="B255" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>135359811</v>
       </c>
       <c r="B256" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>135359812</v>
       </c>
       <c r="B257" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>135359813</v>
       </c>
       <c r="B258" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135359821</v>
       </c>
       <c r="B259" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>135359838</v>
       </c>
       <c r="B260" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>135359851</v>
       </c>
       <c r="B261" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>135363823</v>
       </c>
       <c r="B262" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357743</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135357390</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135357753</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135359820</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135357874</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135357745</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135357881</v>
       </c>
       <c r="B28" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135363826</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>135357752</v>
       </c>
       <c r="B30" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135357856</v>
       </c>
       <c r="B31" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>135357859</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135357873</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>135357875</v>
       </c>
       <c r="B34" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>135357882</v>
       </c>
       <c r="B35" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>135357898</v>
       </c>
       <c r="B36" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>135359825</v>
       </c>
       <c r="B37" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>135357751</v>
       </c>
       <c r="B38" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135359815</v>
       </c>
       <c r="B39" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>135359850</v>
       </c>
       <c r="B51" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135388328</v>
       </c>
       <c r="B52" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>135363827</v>
       </c>
       <c r="B244" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>135357398</v>
       </c>
       <c r="B245" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>135357400</v>
       </c>
       <c r="B246" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>135359822</v>
       </c>
       <c r="B247" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>135357395</v>
       </c>
       <c r="B248" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>135357397</v>
       </c>
       <c r="B249" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>135357399</v>
       </c>
       <c r="B250" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>135357401</v>
       </c>
       <c r="B251" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>135357402</v>
       </c>
       <c r="B252" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>135357403</v>
       </c>
       <c r="B253" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>135357405</v>
       </c>
       <c r="B254" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>135357406</v>
       </c>
       <c r="B255" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>135359811</v>
       </c>
       <c r="B256" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>135359812</v>
       </c>
       <c r="B257" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>135359813</v>
       </c>
       <c r="B258" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135359821</v>
       </c>
       <c r="B259" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>135359838</v>
       </c>
       <c r="B260" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>135359851</v>
       </c>
       <c r="B261" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>135363823</v>
       </c>
       <c r="B262" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>135362040</v>
       </c>
       <c r="B23" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135362050</v>
       </c>
       <c r="B24" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135362060</v>
       </c>
       <c r="B26" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135363826</v>
       </c>
       <c r="B29" t="n">
-        <v>92871</v>
+        <v>92886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>135362032</v>
       </c>
       <c r="B155" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>135363825</v>
       </c>
       <c r="B169" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>135362052</v>
       </c>
       <c r="B193" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>135362037</v>
       </c>
       <c r="B197" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>135362049</v>
       </c>
       <c r="B198" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>135362035</v>
       </c>
       <c r="B228" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>135362042</v>
       </c>
       <c r="B229" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>135362043</v>
       </c>
       <c r="B230" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>135362057</v>
       </c>
       <c r="B231" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>135362059</v>
       </c>
       <c r="B232" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>135362064</v>
       </c>
       <c r="B233" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>135362065</v>
       </c>
       <c r="B234" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>135519109</v>
       </c>
       <c r="B235" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>135363819</v>
       </c>
       <c r="B239" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>135363820</v>
       </c>
       <c r="B242" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>135363827</v>
       </c>
       <c r="B244" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>135363823</v>
       </c>
       <c r="B262" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2025 artfynd.xlsx
+++ b/artfynd/A 29667-2025 artfynd.xlsx
@@ -3131,7 +3131,7 @@
         <v>135362040</v>
       </c>
       <c r="B23" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135362050</v>
       </c>
       <c r="B24" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135362060</v>
       </c>
       <c r="B26" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>135362032</v>
       </c>
       <c r="B155" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>135362052</v>
       </c>
       <c r="B193" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
